--- a/010-npm_node/02-results/2108EP03S Bel Aire Revision 2- Corrected Math.xlsx
+++ b/010-npm_node/02-results/2108EP03S Bel Aire Revision 2- Corrected Math.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
@@ -476,7 +476,7 @@
         <v>CONTRACT_FILE</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -502,10 +502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I3" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J3" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K3" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -514,7 +516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -540,10 +542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I4" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J4" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K4" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -552,7 +556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -578,10 +582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I5" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J5" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K5" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -590,7 +596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -616,10 +622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I6" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J6" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K6" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -628,7 +636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -654,10 +662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I7" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J7" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K7" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -666,7 +676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -692,10 +702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I8" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J8" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K8" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -704,7 +716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -730,10 +742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I9" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J9" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K9" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -742,7 +756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -768,10 +782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I10" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J10" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K10" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -780,7 +796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -806,10 +822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I11" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J11" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K11" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -818,7 +836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -844,10 +862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I12" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J12" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K12" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -856,7 +876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -882,10 +902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I13" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J13" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K13" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -894,7 +916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -920,10 +942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I14" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J14" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K14" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -932,7 +956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -958,10 +982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I15" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J15" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K15" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -970,7 +996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -996,10 +1022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I16" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J16" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K16" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1008,7 +1036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" xml:space="preserve">
       <c r="A17" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1034,10 +1062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I17" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J17" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K17" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1046,7 +1076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1072,10 +1102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I18" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J18" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K18" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1084,7 +1116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1110,10 +1142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I19" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J19" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K19" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1122,7 +1156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1148,10 +1182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I20" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J20" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K20" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1160,7 +1196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1186,10 +1222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I21" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J21" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K21" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1198,7 +1236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1224,10 +1262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I22" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J22" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K22" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1236,7 +1276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1262,10 +1302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I23" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J23" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K23" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1274,7 +1316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1300,10 +1342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I24" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J24" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K24" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1312,7 +1356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1338,10 +1382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I25" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J25" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K25" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1350,7 +1396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1376,10 +1422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I26" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J26" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K26" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1388,7 +1436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1414,10 +1462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I27" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J27" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K27" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1426,7 +1476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1452,10 +1502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I28" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J28" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K28" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1464,7 +1516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1490,10 +1542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I29" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J29" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K29" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1502,7 +1556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1528,10 +1582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I30" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J30" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K30" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1540,7 +1596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1566,10 +1622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I31" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J31" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K31" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1578,7 +1636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1604,10 +1662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I32" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J32" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K32" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1616,7 +1676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" xml:space="preserve">
       <c r="A33" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1642,10 +1702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I33" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J33" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K33" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1654,7 +1716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1680,10 +1742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I34" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J34" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K34" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1692,7 +1756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1718,10 +1782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I35" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J35" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K35" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1730,7 +1796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1756,10 +1822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I36" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J36" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K36" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1768,7 +1836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1794,10 +1862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I37" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J37" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K37" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1806,7 +1876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1832,10 +1902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I38" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J38" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K38" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1844,7 +1916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -1870,10 +1942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I39" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J39" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K39" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1882,7 +1956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" xml:space="preserve">
       <c r="A40" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -1908,10 +1982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I40" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J40" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K40" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1920,7 +1996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -1946,10 +2022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I41" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J41" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K41" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1958,7 +2036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -1984,10 +2062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I42" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J42" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K42" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -1996,7 +2076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2022,10 +2102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I43" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J43" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K43" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2034,7 +2116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" xml:space="preserve">
       <c r="A44" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2060,10 +2142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I44" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J44" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K44" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2072,7 +2156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2098,10 +2182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I45" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J45" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K45" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2110,7 +2196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" xml:space="preserve">
       <c r="A46" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2136,10 +2222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I46" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J46" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K46" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2148,7 +2236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2174,10 +2262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I47" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J47" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K47" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2186,7 +2276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2212,10 +2302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I48" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J48" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K48" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2224,7 +2316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2250,10 +2342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I49" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J49" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K49" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2262,7 +2356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2288,10 +2382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I50" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J50" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K50" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2300,7 +2396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" xml:space="preserve">
       <c r="A51" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
       </c>
@@ -2326,10 +2422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I51" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J51" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K51" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2338,7 +2436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2364,10 +2462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I52" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J52" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K52" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2376,7 +2476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2402,10 +2502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I53" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J53" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K53" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2414,7 +2516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2440,10 +2542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I54" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J54" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K54" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2452,7 +2556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2478,10 +2582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I55" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J55" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K55" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2490,7 +2596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2516,10 +2622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I56" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J56" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K56" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2528,7 +2636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" xml:space="preserve">
       <c r="A57" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2554,10 +2662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I57" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J57" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K57" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2566,7 +2676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" xml:space="preserve">
       <c r="A58" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2592,10 +2702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I58" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J58" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K58" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2604,7 +2716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
       </c>
@@ -2630,10 +2742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I59" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J59" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K59" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2642,7 +2756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2668,10 +2782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I60" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J60" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K60" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2680,7 +2796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2706,10 +2822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I61" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J61" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K61" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2718,7 +2836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2744,10 +2862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I62" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J62" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K62" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2756,7 +2876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2782,10 +2902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I63" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J63" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K63" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2794,7 +2916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2820,10 +2942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I64" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J64" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K64" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2832,7 +2956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" xml:space="preserve">
       <c r="A65" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
       </c>
@@ -2858,10 +2982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I65" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J65" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K65" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2870,7 +2996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" xml:space="preserve">
       <c r="A66" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -2896,10 +3022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I66" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J66" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K66" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2908,7 +3036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" xml:space="preserve">
       <c r="A67" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -2934,10 +3062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I67" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J67" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K67" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2946,7 +3076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" xml:space="preserve">
       <c r="A68" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -2972,10 +3102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I68" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J68" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K68" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -2984,7 +3116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -3010,10 +3142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I69" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J69" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K69" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3022,7 +3156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -3048,10 +3182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I70" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J70" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K70" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3060,7 +3196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" xml:space="preserve">
       <c r="A71" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
       </c>
@@ -3086,10 +3222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I71" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J71" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K71" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3098,7 +3236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" xml:space="preserve">
       <c r="A72" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3124,10 +3262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I72" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J72" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K72" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3136,7 +3276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3162,10 +3302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I73" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J73" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K73" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3174,7 +3316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3200,10 +3342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I74" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J74" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K74" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3212,7 +3356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3238,10 +3382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I75" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J75" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K75" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3250,7 +3396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" xml:space="preserve">
       <c r="A76" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3276,10 +3422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I76" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J76" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K76" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3288,7 +3436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
       </c>
@@ -3314,10 +3462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I77" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J77" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K77" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3326,7 +3476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" xml:space="preserve">
       <c r="A78" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3352,10 +3502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I78" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J78" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K78" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3364,7 +3516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" xml:space="preserve">
       <c r="A79" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3390,10 +3542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I79" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J79" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K79" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3402,7 +3556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" xml:space="preserve">
       <c r="A80" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3428,10 +3582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I80" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J80" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K80" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3440,7 +3596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3466,10 +3622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I81" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J81" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K81" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3478,7 +3636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" xml:space="preserve">
       <c r="A82" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3504,10 +3662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I82" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J82" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K82" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3516,7 +3676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" xml:space="preserve">
       <c r="A83" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3542,10 +3702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I83" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J83" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K83" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3554,7 +3716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" xml:space="preserve">
       <c r="A84" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
       </c>
@@ -3580,10 +3742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I84" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J84" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K84" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3592,7 +3756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
       </c>
@@ -3618,10 +3782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I85" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J85" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K85" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3630,7 +3796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
       </c>
@@ -3656,10 +3822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I86" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J86" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K86" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3668,7 +3836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" xml:space="preserve">
       <c r="A87" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
       </c>
@@ -3694,10 +3862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I87" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J87" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K87" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3706,7 +3876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" xml:space="preserve">
       <c r="A88" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
       </c>
@@ -3732,10 +3902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I88" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J88" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K88" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3744,7 +3916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" xml:space="preserve">
       <c r="A89" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
       </c>
@@ -3770,10 +3942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I89" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J89" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K89" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3782,7 +3956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" xml:space="preserve">
       <c r="A90" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3808,10 +3982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I90" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J90" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K90" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3820,7 +3996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3846,10 +4022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I91" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J91" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K91" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3858,7 +4036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" xml:space="preserve">
       <c r="A92" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3884,10 +4062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I92" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J92" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K92" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3896,7 +4076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" xml:space="preserve">
       <c r="A93" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3922,10 +4102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I93" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J93" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K93" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3934,7 +4116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3960,10 +4142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I94" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J94" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K94" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -3972,7 +4156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" xml:space="preserve">
       <c r="A95" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -3998,10 +4182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I95" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J95" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K95" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4010,7 +4196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -4036,10 +4222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I96" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J96" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K96" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4048,7 +4236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -4074,10 +4262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I97" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J97" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K97" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4086,7 +4276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" xml:space="preserve">
       <c r="A98" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -4112,10 +4302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I98" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J98" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K98" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4124,7 +4316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" xml:space="preserve">
       <c r="A99" t="str">
         <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
       </c>
@@ -4150,10 +4342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I99" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J99" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K99" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4162,7 +4356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" xml:space="preserve">
       <c r="A100" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4188,10 +4382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I100" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J100" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K100" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4200,7 +4396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" xml:space="preserve">
       <c r="A101" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4226,10 +4422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I101" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J101" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K101" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4238,7 +4436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4264,10 +4462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I102" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J102" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K102" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4276,7 +4476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4302,10 +4502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I103" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J103" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K103" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4314,7 +4516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4340,10 +4542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I104" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J104" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K104" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4352,7 +4556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" xml:space="preserve">
       <c r="A105" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4378,10 +4582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I105" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J105" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K105" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4390,7 +4596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" xml:space="preserve">
       <c r="A106" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4416,10 +4622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I106" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J106" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K106" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4428,7 +4636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" xml:space="preserve">
       <c r="A107" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4454,10 +4662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I107" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J107" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K107" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4466,7 +4676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" xml:space="preserve">
       <c r="A108" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4492,10 +4702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I108" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J108" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K108" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4504,7 +4716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" xml:space="preserve">
       <c r="A109" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4530,10 +4742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I109" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J109" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K109" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4542,7 +4756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" xml:space="preserve">
       <c r="A110" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4568,10 +4782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I110" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J110" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K110" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4580,7 +4796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" xml:space="preserve">
       <c r="A111" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4606,10 +4822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I111" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J111" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K111" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4618,7 +4836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4644,10 +4862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I112" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J112" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J112" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K112" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4656,7 +4876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" xml:space="preserve">
       <c r="A113" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4682,10 +4902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I113" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J113" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J113" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K113" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4694,7 +4916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" xml:space="preserve">
       <c r="A114" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4720,10 +4942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I114" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J114" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J114" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K114" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4732,7 +4956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" xml:space="preserve">
       <c r="A115" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4758,10 +4982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I115" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J115" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J115" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K115" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4770,7 +4996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" xml:space="preserve">
       <c r="A116" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4796,10 +5022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I116" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J116" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J116" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K116" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4808,7 +5036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4834,10 +5062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I117" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J117" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J117" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K117" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4846,7 +5076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" xml:space="preserve">
       <c r="A118" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4872,10 +5102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I118" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J118" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J118" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K118" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4884,7 +5116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" xml:space="preserve">
       <c r="A119" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4910,10 +5142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I119" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J119" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J119" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K119" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4922,7 +5156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" xml:space="preserve">
       <c r="A120" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4948,10 +5182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I120" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J120" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J120" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K120" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4960,7 +5196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" xml:space="preserve">
       <c r="A121" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -4986,10 +5222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I121" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J121" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J121" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K121" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -4998,7 +5236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" xml:space="preserve">
       <c r="A122" t="str">
         <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
       </c>
@@ -5024,10 +5262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I122" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J122" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J122" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K122" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5036,7 +5276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" xml:space="preserve">
       <c r="A123" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
       </c>
@@ -5062,10 +5302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I123" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J123" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J123" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K123" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5074,7 +5316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" xml:space="preserve">
       <c r="A124" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
       </c>
@@ -5100,10 +5342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I124" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J124" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J124" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K124" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5112,7 +5356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" xml:space="preserve">
       <c r="A125" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
       </c>
@@ -5138,10 +5382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I125" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J125" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J125" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K125" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5150,7 +5396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" xml:space="preserve">
       <c r="A126" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
       </c>
@@ -5176,10 +5422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I126" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J126" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J126" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K126" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5188,7 +5436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" xml:space="preserve">
       <c r="A127" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
       </c>
@@ -5214,10 +5462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I127" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J127" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J127" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K127" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5226,7 +5476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" xml:space="preserve">
       <c r="A128" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5252,10 +5502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I128" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J128" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J128" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K128" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5264,7 +5516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" xml:space="preserve">
       <c r="A129" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5290,10 +5542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I129" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J129" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J129" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K129" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5302,7 +5556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" xml:space="preserve">
       <c r="A130" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5328,10 +5582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I130" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J130" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J130" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K130" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5340,7 +5596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" xml:space="preserve">
       <c r="A131" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5366,10 +5622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I131" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J131" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J131" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K131" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5378,7 +5636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" xml:space="preserve">
       <c r="A132" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5404,10 +5662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I132" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J132" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J132" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K132" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5416,7 +5676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" xml:space="preserve">
       <c r="A133" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5442,10 +5702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I133" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J133" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J133" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K133" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5454,7 +5716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" xml:space="preserve">
       <c r="A134" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5480,10 +5742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I134" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J134" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J134" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K134" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5492,7 +5756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" xml:space="preserve">
       <c r="A135" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5518,10 +5782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I135" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J135" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J135" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K135" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5530,7 +5796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" xml:space="preserve">
       <c r="A136" t="str">
         <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5556,10 +5822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I136" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J136" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J136" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K136" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5568,7 +5836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" xml:space="preserve">
       <c r="A137" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5594,10 +5862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I137" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J137" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J137" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K137" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5606,7 +5876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" xml:space="preserve">
       <c r="A138" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5632,10 +5902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I138" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J138" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J138" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K138" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5644,7 +5916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" xml:space="preserve">
       <c r="A139" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5670,10 +5942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I139" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J139" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J139" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K139" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5682,7 +5956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" xml:space="preserve">
       <c r="A140" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5708,10 +5982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I140" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J140" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J140" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K140" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5720,7 +5996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" xml:space="preserve">
       <c r="A141" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5746,10 +6022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I141" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J141" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J141" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K141" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5758,7 +6036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" xml:space="preserve">
       <c r="A142" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5784,10 +6062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I142" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J142" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J142" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K142" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5796,7 +6076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5822,10 +6102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I143" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J143" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J143" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K143" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5834,7 +6116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" xml:space="preserve">
       <c r="A144" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5860,10 +6142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I144" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J144" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J144" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K144" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5872,7 +6156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" xml:space="preserve">
       <c r="A145" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5898,10 +6182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I145" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J145" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J145" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K145" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5910,7 +6196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" xml:space="preserve">
       <c r="A146" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5936,10 +6222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I146" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J146" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J146" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K146" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5948,7 +6236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" xml:space="preserve">
       <c r="A147" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -5974,10 +6262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I147" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J147" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J147" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K147" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -5986,7 +6276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" xml:space="preserve">
       <c r="A148" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -6012,10 +6302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I148" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J148" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J148" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K148" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6024,7 +6316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" xml:space="preserve">
       <c r="A149" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -6050,10 +6342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I149" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J149" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J149" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K149" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6062,7 +6356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" xml:space="preserve">
       <c r="A150" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -6088,10 +6382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I150" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J150" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J150" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K150" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6100,7 +6396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" xml:space="preserve">
       <c r="A151" t="str">
         <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
       </c>
@@ -6126,10 +6422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I151" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J151" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J151" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K151" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6138,7 +6436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" xml:space="preserve">
       <c r="A152" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6164,10 +6462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I152" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J152" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J152" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K152" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6176,7 +6476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" xml:space="preserve">
       <c r="A153" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6202,10 +6502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I153" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J153" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J153" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K153" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6214,7 +6516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" xml:space="preserve">
       <c r="A154" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6240,10 +6542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I154" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J154" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J154" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K154" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6252,7 +6556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" xml:space="preserve">
       <c r="A155" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6278,10 +6582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I155" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J155" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J155" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K155" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6290,7 +6596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" xml:space="preserve">
       <c r="A156" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6316,10 +6622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I156" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J156" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J156" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K156" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6328,7 +6636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" xml:space="preserve">
       <c r="A157" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6354,10 +6662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I157" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J157" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J157" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K157" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6366,7 +6676,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" xml:space="preserve">
       <c r="A158" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6392,10 +6702,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I158" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J158" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J158" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K158" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6404,7 +6716,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" xml:space="preserve">
       <c r="A159" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6430,10 +6742,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I159" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J159" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J159" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K159" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6442,7 +6756,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" xml:space="preserve">
       <c r="A160" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6468,10 +6782,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I160" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J160" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J160" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K160" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6480,7 +6796,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" xml:space="preserve">
       <c r="A161" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6506,10 +6822,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I161" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J161" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J161" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K161" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6518,7 +6836,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" xml:space="preserve">
       <c r="A162" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6544,10 +6862,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I162" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J162" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J162" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K162" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6556,7 +6876,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" xml:space="preserve">
       <c r="A163" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6582,10 +6902,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I163" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J163" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J163" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K163" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6594,7 +6916,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" xml:space="preserve">
       <c r="A164" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6620,10 +6942,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I164" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J164" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J164" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K164" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6632,7 +6956,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" xml:space="preserve">
       <c r="A165" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
       </c>
@@ -6658,10 +6982,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I165" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J165" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J165" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K165" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6670,7 +6996,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" xml:space="preserve">
       <c r="A166" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6696,10 +7022,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I166" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J166" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J166" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K166" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6708,7 +7036,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" xml:space="preserve">
       <c r="A167" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6734,10 +7062,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I167" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J167" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J167" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K167" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6746,7 +7076,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" xml:space="preserve">
       <c r="A168" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6772,10 +7102,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I168" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J168" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J168" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K168" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6784,7 +7116,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" xml:space="preserve">
       <c r="A169" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6810,10 +7142,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I169" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J169" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J169" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K169" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6822,7 +7156,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" xml:space="preserve">
       <c r="A170" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6848,10 +7182,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I170" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J170" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J170" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K170" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6860,7 +7196,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" xml:space="preserve">
       <c r="A171" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6886,10 +7222,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I171" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J171" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J171" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K171" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6898,7 +7236,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" xml:space="preserve">
       <c r="A172" t="str">
         <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
       </c>
@@ -6924,10 +7262,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I172" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J172" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J172" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K172" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6936,7 +7276,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" xml:space="preserve">
       <c r="A173" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -6962,10 +7302,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I173" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J173" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J173" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K173" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -6974,7 +7316,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" xml:space="preserve">
       <c r="A174" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7000,10 +7342,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I174" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J174" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J174" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K174" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7012,7 +7356,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" xml:space="preserve">
       <c r="A175" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7038,10 +7382,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I175" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J175" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J175" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K175" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7050,7 +7396,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" xml:space="preserve">
       <c r="A176" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7076,10 +7422,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I176" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J176" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J176" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K176" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7088,7 +7436,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" xml:space="preserve">
       <c r="A177" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7114,10 +7462,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I177" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J177" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J177" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K177" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7126,7 +7476,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" xml:space="preserve">
       <c r="A178" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7152,10 +7502,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I178" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J178" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J178" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K178" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7164,7 +7516,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" xml:space="preserve">
       <c r="A179" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7190,10 +7542,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I179" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J179" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J179" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K179" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7202,7 +7556,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" xml:space="preserve">
       <c r="A180" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7228,10 +7582,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I180" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J180" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J180" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K180" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7240,7 +7596,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" xml:space="preserve">
       <c r="A181" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7266,10 +7622,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I181" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J181" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J181" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K181" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
@@ -7278,7 +7636,7 @@
         <v>2108EP03S Bel Aire Revision 2- Corrected Math.xlsx</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" xml:space="preserve">
       <c r="A182" t="str">
         <v>#15: AMENITY SIGNAGE</v>
       </c>
@@ -7304,10 +7662,12 @@
         <v>JENNA STOELTJE STAMPS</v>
       </c>
       <c r="I182" t="str">
-        <v>2108EP03S *** THIS ONE INCLUDES THE COMPREHENSIVE SIGN SUBMITTAL FEE OF $1800. THE ONE WE WILL BE CONTRACTED FOR, IT'S NOT INCLUDED ON THE EXCEL TOTAL</v>
-      </c>
-      <c r="J182" t="str">
-        <v>08.24.03 10.31.23 REVISION 1 11.01.23 REVISION 2</v>
+        <v xml:space="preserve">2108EP03S </v>
+      </c>
+      <c r="J182" t="str" xml:space="preserve">
+        <v xml:space="preserve">08.24.03 10.31.23 REVISION 1
+ 11.01.23 REVISION 2
+</v>
       </c>
       <c r="K182" t="str">
         <v>BEL AIRE (COLFAX &amp; OWENS)</v>
